--- a/vulnerability/kamailio_漏洞发现_20260607170503.xlsx
+++ b/vulnerability/kamailio_漏洞发现_20260607170503.xlsx
@@ -69,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -78,6 +78,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -445,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J344"/>
+  <dimension ref="A1:K344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -458,6 +461,7 @@
     <col width="75" customWidth="1" min="8" max="8"/>
     <col width="35" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,6 +513,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>为什么算漏洞</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>漏洞带来的影响</t>
         </is>
       </c>
     </row>
@@ -632,6 +641,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -753,6 +770,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -874,6 +899,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -995,6 +1028,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1114,6 +1155,14 @@
 6. 同类CVE-2020-27507(CVSS 9.8)佐证kamailio SIP处理的内存安全缺陷
 7. 影响SIP核心协议处理路径，可导致远程拒绝服务(DoS)或潜在的远程代码执行(RCE)
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -1230,6 +1279,11 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1342,6 +1396,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -1461,6 +1520,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1572,6 +1639,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -1688,6 +1763,11 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1799,6 +1879,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -1913,6 +1999,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -2032,6 +2123,13 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2143,6 +2241,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -2267,6 +2371,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2378,6 +2492,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -2502,6 +2624,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2614,6 +2747,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -2733,6 +2871,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2847,6 +2993,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -2964,6 +3120,13 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -3092,6 +3255,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -3205,6 +3378,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -3316,6 +3497,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -3437,6 +3624,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3548,6 +3745,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -3666,6 +3871,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3778,6 +3994,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -3894,6 +4115,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -4011,6 +4240,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -4135,6 +4372,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -4249,6 +4497,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -4373,6 +4631,19 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -4488,6 +4759,13 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -4607,6 +4885,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -4735,6 +5023,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -4857,6 +5155,19 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -4978,6 +5289,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -5099,6 +5418,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -5220,6 +5547,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -5339,6 +5674,14 @@
 6. 同类CVE-2020-27507(CVSS 9.8)佐证kamailio SIP处理的内存安全缺陷
 7. 影响SIP核心协议处理路径，可导致远程拒绝服务(DoS)或潜在的远程代码执行(RCE)
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -5455,6 +5798,11 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -5569,6 +5917,11 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -5680,6 +6033,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -5794,6 +6155,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -5913,6 +6279,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -6024,6 +6398,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -6142,6 +6522,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -6253,6 +6643,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -6371,6 +6769,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -6483,6 +6892,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -6608,6 +7022,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -6725,6 +7147,13 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -6839,6 +7268,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -6950,6 +7387,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -7068,6 +7511,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -7179,6 +7632,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -7297,6 +7758,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -7409,6 +7881,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -7526,6 +8003,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -7653,6 +8138,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -7768,6 +8263,13 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -7887,6 +8389,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -8012,6 +8524,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -8134,6 +8656,19 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -8255,6 +8790,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -8376,6 +8919,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -8497,6 +9048,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -8618,6 +9177,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -8739,6 +9306,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -8852,6 +9427,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -8963,6 +9546,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -9079,6 +9670,11 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -9190,6 +9786,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -9308,6 +9912,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -9419,6 +10031,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -9537,6 +10157,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -9651,6 +10282,11 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -9764,6 +10400,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -9875,6 +10519,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -9993,6 +10645,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -10107,6 +10770,11 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -10220,6 +10888,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -10331,6 +11007,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -10449,6 +11131,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -10560,6 +11252,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -10678,6 +11378,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -10790,6 +11501,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -10911,6 +11627,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -11026,6 +11750,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -11147,6 +11879,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -11261,6 +12004,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -11385,6 +12138,19 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -11500,6 +12266,13 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -11619,6 +12392,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -11739,6 +12522,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -11872,6 +12665,19 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -11993,6 +12799,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -12114,6 +12928,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -12235,6 +13057,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -12354,6 +13184,14 @@
 6. 同类CVE-2020-27507(CVSS 9.8)佐证kamailio SIP处理的内存安全缺陷
 7. 影响SIP核心协议处理路径，可导致远程拒绝服务(DoS)或潜在的远程代码执行(RCE)
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -12470,6 +13308,11 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -12582,6 +13425,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -12707,6 +13555,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -12818,6 +13674,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -12934,6 +13798,11 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -13045,6 +13914,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -13159,6 +14034,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -13278,6 +14158,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -13394,6 +14282,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -13510,6 +14406,12 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -13626,6 +14528,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -13737,6 +14649,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -13855,6 +14775,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -13967,6 +14898,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -14083,6 +15019,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -14200,6 +15144,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K118" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -14327,6 +15279,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -14441,6 +15404,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -14565,6 +15538,19 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -14680,6 +15666,13 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K122" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -14799,6 +15792,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -14922,6 +15925,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -15049,6 +16062,19 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -15170,6 +16196,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K126" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -15291,6 +16325,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K127" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -15412,6 +16454,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K128" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -15533,6 +16583,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K129" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -15654,6 +16712,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K130" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -15773,6 +16839,14 @@
 6. 同类CVE-2020-27507(CVSS 9.8)佐证kamailio SIP处理的内存安全缺陷
 7. 影响SIP核心协议处理路径，可导致远程拒绝服务(DoS)或潜在的远程代码执行(RCE)
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
+        </is>
+      </c>
+      <c r="K131" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -15889,6 +16963,11 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -16001,6 +17080,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K133" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -16120,6 +17204,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K134" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -16231,6 +17323,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -16345,6 +17443,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K136" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -16464,6 +17567,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K137" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -16575,6 +17686,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K138" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -16693,6 +17812,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K139" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -16804,6 +17931,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K140" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -16922,6 +18057,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K141" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -17038,6 +18184,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K142" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -17149,6 +18303,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -17267,6 +18427,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -17378,6 +18548,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -17496,6 +18674,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K146" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -17608,6 +18797,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K147" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -17724,6 +18918,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -17846,6 +19048,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -17965,6 +19175,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -18079,6 +19300,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K151" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -18203,6 +19434,19 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K152" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -18318,6 +19562,13 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K153" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -18437,6 +19688,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K154" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -18565,6 +19826,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -18690,6 +19961,19 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K156" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -18811,6 +20095,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K157" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -18945,6 +20237,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K158" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -19066,6 +20366,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K159" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -19187,6 +20495,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K160" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -19308,6 +20624,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K161" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -19429,6 +20753,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K162" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -19548,6 +20880,14 @@
 6. 同类CVE-2020-27507(CVSS 9.8)佐证kamailio SIP处理的内存安全缺陷
 7. 影响SIP核心协议处理路径，可导致远程拒绝服务(DoS)或潜在的远程代码执行(RCE)
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
+        </is>
+      </c>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -19662,6 +21002,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K164" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -19781,6 +21126,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K165" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -19892,6 +21245,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K166" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -20010,6 +21369,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K167" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -20122,6 +21491,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K168" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -20241,6 +21615,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K169" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -20358,6 +21740,13 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K170" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -20469,6 +21858,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K171" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -20587,6 +21982,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K172" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -20700,6 +22105,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K173" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -20811,6 +22224,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K174" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -20932,6 +22351,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K175" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -21043,6 +22472,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K176" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -21157,6 +22594,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K177" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -21279,6 +22721,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K178" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -21394,6 +22844,13 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K179" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -21516,6 +22973,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K180" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -21632,6 +23099,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K181" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -21743,6 +23218,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K182" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -21861,6 +23342,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K183" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -21972,6 +23463,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K184" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -22093,6 +23592,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K185" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -22205,6 +23715,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K186" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -22321,6 +23836,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K187" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -22440,6 +23963,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K188" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -22554,6 +24085,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K189" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -22678,6 +24219,19 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K190" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -22793,6 +24347,13 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K191" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -22926,6 +24487,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K192" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -23044,6 +24615,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K193" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -23171,6 +24752,19 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K194" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -23292,6 +24886,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K195" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -23413,6 +25015,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K196" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -23534,6 +25144,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K197" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -23655,6 +25273,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K198" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -23776,6 +25402,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K199" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -23897,6 +25531,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K200" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -24018,6 +25660,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K201" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -24139,6 +25789,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K202" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -24260,6 +25918,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K203" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -24381,6 +26047,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K204" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -24502,6 +26176,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K205" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -24623,6 +26305,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K206" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -24744,6 +26434,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K207" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -24865,6 +26563,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K208" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -25000,6 +26706,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K209" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -25126,6 +26840,14 @@
 6. 同类CVE-2020-27507(CVSS 9.8)佐证kamailio SIP处理的内存安全缺陷
 7. 影响SIP核心协议处理路径，可导致远程拒绝服务(DoS)或潜在的远程代码执行(RCE)
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
+        </is>
+      </c>
+      <c r="K210" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -25242,6 +26964,11 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K211" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -25354,6 +27081,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K212" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -25473,6 +27205,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K213" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -25584,6 +27324,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K214" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -25702,6 +27448,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K215" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -25814,6 +27570,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K216" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -25933,6 +27694,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K217" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -26050,6 +27819,13 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K218" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -26161,6 +27937,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K219" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -26279,6 +28061,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K220" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -26390,6 +28182,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K221" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -26504,6 +28304,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K222" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -26623,6 +28428,13 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K223" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -26736,6 +28548,12 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K224" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -26847,6 +28665,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K225" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -26965,6 +28791,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K226" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -27079,6 +28913,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K227" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -27200,6 +29040,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K228" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -27311,6 +29161,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K229" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -27429,6 +29287,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K230" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -27541,6 +29410,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K231" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -27657,6 +29531,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K232" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -27774,6 +29656,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K233" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -27901,6 +29791,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K234" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -28015,6 +29916,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K235" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -28134,6 +30045,19 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K236" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -28254,6 +30178,13 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K237" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -28376,6 +30307,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K238" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -28507,6 +30448,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K239" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -28635,6 +30586,19 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K240" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -28756,6 +30720,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K241" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -28877,6 +30849,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K242" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -28998,6 +30978,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K243" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -29119,6 +31107,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K244" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -29240,6 +31236,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K245" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -29361,6 +31365,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K246" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -29482,6 +31494,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K247" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -29603,6 +31623,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K248" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -29724,6 +31752,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K249" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -29845,6 +31881,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K250" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -29966,6 +32010,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K251" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -30087,6 +32139,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K252" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -30206,6 +32266,14 @@
 6. 同类CVE-2020-27507(CVSS 9.8)佐证kamailio SIP处理的内存安全缺陷
 7. 影响SIP核心协议处理路径，可导致远程拒绝服务(DoS)或潜在的远程代码执行(RCE)
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
+        </is>
+      </c>
+      <c r="K253" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -30320,6 +32388,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K254" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -30439,6 +32512,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K255" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -30550,6 +32631,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K256" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -30668,6 +32755,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K257" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -30782,6 +32879,11 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K258" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -30893,6 +32995,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K259" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -31011,6 +33119,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K260" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -31123,6 +33241,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K261" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -31239,6 +33365,11 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K262" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -31350,6 +33481,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K263" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -31468,6 +33605,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K264" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -31579,6 +33726,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K265" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -31697,6 +33852,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K266" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -31809,6 +33975,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K267" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -31931,6 +34102,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K268" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -32045,6 +34224,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K269" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -32164,6 +34353,13 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K270" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -32277,6 +34473,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K271" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -32388,6 +34592,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K272" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -32502,6 +34712,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K273" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -32613,6 +34833,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K274" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -32737,6 +34965,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K275" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -32849,6 +35088,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K276" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -32970,6 +35214,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K277" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -33085,6 +35337,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K278" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -33206,6 +35466,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K279" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -33320,6 +35591,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K280" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -33450,6 +35731,19 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K281" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -33565,6 +35859,13 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K282" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -33684,6 +35985,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K283" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -33815,6 +36126,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K284" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -33936,6 +36257,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K285" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -34057,6 +36386,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K286" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -34178,6 +36515,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K287" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -34297,6 +36642,14 @@
 6. 同类CVE-2020-27507(CVSS 9.8)佐证kamailio SIP处理的内存安全缺陷
 7. 影响SIP核心协议处理路径，可导致远程拒绝服务(DoS)或潜在的远程代码执行(RCE)
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
+        </is>
+      </c>
+      <c r="K288" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -34413,6 +36766,11 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K289" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -34525,6 +36883,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K290" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -34644,6 +37007,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K291" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -34755,6 +37126,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K292" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -34871,6 +37250,11 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K293" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -34982,6 +37366,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K294" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -35100,6 +37490,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K295" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -35212,6 +37612,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K296" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -35334,6 +37739,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K297" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -35452,6 +37865,13 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K298" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -35580,6 +38000,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K299" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -35691,6 +38121,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K300" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -35809,6 +38245,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K301" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -35920,6 +38366,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K302" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -36038,6 +38492,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K303" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -36150,6 +38615,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K304" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -36266,6 +38736,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K305" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -36388,6 +38866,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K306" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -36502,6 +38988,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K307" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -36626,6 +39122,19 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K308" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -36746,6 +39255,13 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K309" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -36866,6 +39382,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K310" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -36985,6 +39511,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K311" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -37099,6 +39633,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K312" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -37220,6 +39760,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K313" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -37331,6 +39881,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K314" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -37455,6 +40013,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K315" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -37567,6 +40136,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K316" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -37683,6 +40257,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K317" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -37802,6 +40384,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K318" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -37916,6 +40506,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K319" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -38046,6 +40646,19 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K320" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -38161,6 +40774,13 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K321" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -38286,6 +40906,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K322" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -38407,6 +41037,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K323" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -38528,6 +41166,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K324" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -38649,6 +41295,14 @@
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
         </is>
       </c>
+      <c r="K325" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -38768,6 +41422,14 @@
 6. 同类CVE-2020-27507(CVSS 9.8)佐证kamailio SIP处理的内存安全缺陷
 7. 影响SIP核心协议处理路径，可导致远程拒绝服务(DoS)或潜在的远程代码执行(RCE)
 8. 10组独立fuzzing实验交叉验证，62个独特崩溃hash证明缺陷广泛</t>
+        </is>
+      </c>
+      <c r="K326" s="4" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发Kamailio堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致Kamailio进程崩溃退出，造成服务不可用。若Kamailio未配置自动重启或watchdog，服务将永久中断。
+【严重级别确证】该漏洞对应的CVE模式CVSS评分为9.0+（严重级别），确认此漏洞可造成系统完全失陷的最严重后果。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -38884,6 +41546,11 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K327" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -38996,6 +41663,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K328" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -39118,6 +41790,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K329" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -39232,6 +41912,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K330" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -39357,6 +42045,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K331" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -39468,6 +42164,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K332" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -39582,6 +42284,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K333" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -39700,6 +42407,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K334" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -39811,6 +42526,12 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K335" s="4" t="inlineStr">
+        <is>
+          <t>【内存耗尽型拒绝服务】攻击者可向Kamailio发送特制的超长协议字段或大量并发请求，导致服务器内存分配持续增长直至OOM(Out of Memory)。操作系统OOM Killer将强制终止Kamailio进程，造成服务完全中断。在容器化部署环境中，可能触发Pod/容器重启，影响同节点其他服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -39929,6 +42650,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K336" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -40040,6 +42771,14 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K337" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -40158,6 +42897,17 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K338" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -40270,6 +43020,11 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K339" s="4" t="inlineStr">
+        <is>
+          <t>【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -40398,6 +43153,14 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K340" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -40512,6 +43275,16 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K341" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -40636,6 +43409,19 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K342" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【未授权访问】攻击者可绕过Kamailio的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将Kamailio的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除Kamailio管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若Kamailio连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -40751,6 +43537,13 @@
 6. 影响SIP服务的核心安全属性(认证/完整性/可用性)
 7. 10组独立实验交叉验证同类违规系统性存在
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
+        </is>
+      </c>
+      <c r="K343" s="4" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -40879,6 +43672,16 @@
 8. 种子经AFLNet多次重放确认为可复现(replayable)</t>
         </is>
       </c>
+      <c r="K344" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】Kamailio的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使Kamailio进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗Kamailio的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
